--- a/docs/工作/10-市场与竞品/小红书面膜竞品对标表.xlsx
+++ b/docs/工作/10-市场与竞品/小红书面膜竞品对标表.xlsx
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,8 +95,13 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -118,11 +123,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -158,6 +207,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -591,11 +645,11 @@
           <t>① 基础信息 / 品牌定位</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="15" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -608,7 +662,11 @@
           <t>日系药妆·平价大盒每日面膜</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>日系国民平价·大盒「每日面膜」，Cosme大赏常客(样本称连续6年日本销量TOP1)</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
@@ -624,7 +682,11 @@
           <t>日本进口·普通化妆品</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>日本进口 · 普通化妆品</t>
+        </is>
+      </c>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
@@ -640,7 +702,11 @@
           <t>学生党/职场女性·追求性价比补水</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr"/>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>学生/职场女性/赴日游客·代购；追求平价补水、按肤质选</t>
+        </is>
+      </c>
       <c r="D7" s="8" t="inlineStr"/>
       <c r="E7" s="8" t="inlineStr"/>
       <c r="F7" s="8" t="inlineStr"/>
@@ -652,7 +718,11 @@
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="8" t="inlineStr"/>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>样本未见强官方号，以素人博主自来水为主(待核实是否有蓝V)</t>
+        </is>
+      </c>
       <c r="D8" s="8" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr"/>
       <c r="F8" s="8" t="inlineStr"/>
@@ -664,7 +734,11 @@
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="8" t="inlineStr"/>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>样本为KOC分散，无头部账号数据(待蒲公英/千瓜补)</t>
+        </is>
+      </c>
       <c r="D9" s="8" t="inlineStr"/>
       <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" s="8" t="inlineStr"/>
@@ -676,7 +750,11 @@
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="8" t="inlineStr"/>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>抓取样本87篇(非全量)；82图文+5视频</t>
+        </is>
+      </c>
       <c r="D10" s="8" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr"/>
       <c r="F10" s="8" t="inlineStr"/>
@@ -688,7 +766,11 @@
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>2025年28篇、2026年50篇，7月最密集(夏季旺季)</t>
+        </is>
+      </c>
       <c r="D11" s="8" t="inlineStr"/>
       <c r="E11" s="8" t="inlineStr"/>
       <c r="F11" s="8" t="inlineStr"/>
@@ -700,7 +782,11 @@
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr"/>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>素人KOC铺量为主(82博主/87篇，一人一篇，无矩阵)</t>
+        </is>
+      </c>
       <c r="D12" s="8" t="inlineStr"/>
       <c r="E12" s="8" t="inlineStr"/>
       <c r="F12" s="8" t="inlineStr"/>
@@ -711,11 +797,11 @@
           <t>② 产品 / 价格</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="15" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -728,7 +814,11 @@
           <t>皇后菁纯 All-in-one 面膜</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>按颜色分系列：紫=抗衰 黄=VC提亮 黑=富勒烯清洁 绿=控油 粉=妆前补水 红/白=驻颜</t>
+        </is>
+      </c>
       <c r="D14" s="8" t="inlineStr"/>
       <c r="E14" s="8" t="inlineStr"/>
       <c r="F14" s="8" t="inlineStr"/>
@@ -744,7 +834,11 @@
           <t>补水保湿·多效合一</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>补水保湿为绝对主诉求(补水82/保湿62)，其次毛孔/提亮/抗老</t>
+        </is>
+      </c>
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="8" t="inlineStr"/>
@@ -756,7 +850,11 @@
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr"/>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>富勒烯、壬二酸衍生物、烟酰胺、谷胱甘肽、维C、聚谷氨酸</t>
+        </is>
+      </c>
       <c r="D16" s="8" t="inlineStr"/>
       <c r="E16" s="8" t="inlineStr"/>
       <c r="F16" s="8" t="inlineStr"/>
@@ -772,7 +870,11 @@
           <t>多片大盒装</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr"/>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>大盒抽拉式，多为7片/盒(主打天天敷)</t>
+        </is>
+      </c>
       <c r="D17" s="8" t="inlineStr"/>
       <c r="E17" s="8" t="inlineStr"/>
       <c r="F17" s="8" t="inlineStr"/>
@@ -784,7 +886,11 @@
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr"/>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>待补(市场约数元/片，数据表无价格字段)</t>
+        </is>
+      </c>
       <c r="D18" s="8" t="inlineStr"/>
       <c r="E18" s="8" t="inlineStr"/>
       <c r="F18" s="8" t="inlineStr"/>
@@ -796,7 +902,11 @@
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr"/>
-      <c r="C19" s="8" t="inlineStr"/>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>待补(数据表无价格字段)</t>
+        </is>
+      </c>
       <c r="D19" s="8" t="inlineStr"/>
       <c r="E19" s="8" t="inlineStr"/>
       <c r="F19" s="8" t="inlineStr"/>
@@ -808,7 +918,11 @@
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr"/>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
       <c r="D20" s="8" t="inlineStr"/>
       <c r="E20" s="8" t="inlineStr"/>
       <c r="F20" s="8" t="inlineStr"/>
@@ -824,7 +938,11 @@
           <t>平价(性价比)</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr"/>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>平价(性价比/伴手礼定位)</t>
+        </is>
+      </c>
       <c r="D21" s="8" t="inlineStr"/>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="8" t="inlineStr"/>
@@ -835,11 +953,11 @@
           <t>③ 内容(小红书胜负手)</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="15" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -848,7 +966,11 @@
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="8" t="inlineStr"/>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>图文合集为主(82/87)；视频仅5篇=洼地</t>
+        </is>
+      </c>
       <c r="D23" s="8" t="inlineStr"/>
       <c r="E23" s="8" t="inlineStr"/>
       <c r="F23" s="8" t="inlineStr"/>
@@ -860,7 +982,11 @@
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="8" t="inlineStr"/>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>🇯🇵国旗+品牌+『怎么选/一篇看懂/不踩雷』+『平价/最便宜』钩子</t>
+        </is>
+      </c>
       <c r="D24" s="8" t="inlineStr"/>
       <c r="E24" s="8" t="inlineStr"/>
       <c r="F24" s="8" t="inlineStr"/>
@@ -872,7 +998,11 @@
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="8" t="inlineStr"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>大字报式：产品平铺实拍+大标题字</t>
+        </is>
+      </c>
       <c r="D25" s="8" t="inlineStr"/>
       <c r="E25" s="8" t="inlineStr"/>
       <c r="F25" s="8" t="inlineStr"/>
@@ -884,7 +1014,11 @@
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="8" t="inlineStr"/>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>#lululun面膜 #面膜测评 #面膜分享 #补水面膜 #保湿面膜 #日本药妆店 #平价面膜</t>
+        </is>
+      </c>
       <c r="D26" s="8" t="inlineStr"/>
       <c r="E26" s="8" t="inlineStr"/>
       <c r="F26" s="8" t="inlineStr"/>
@@ -896,7 +1030,11 @@
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr"/>
-      <c r="C27" s="8" t="inlineStr"/>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>晚间18-21点集中；月度7月高峰</t>
+        </is>
+      </c>
       <c r="D27" s="8" t="inlineStr"/>
       <c r="E27" s="8" t="inlineStr"/>
       <c r="F27" s="8" t="inlineStr"/>
@@ -907,11 +1045,11 @@
           <t>④ 达人 / 投放</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="15" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -920,7 +1058,11 @@
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="8" t="inlineStr"/>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>素人KOC铺量为主，无头部集中(样本82博主几乎一人一篇)</t>
+        </is>
+      </c>
       <c r="D29" s="8" t="inlineStr"/>
       <c r="E29" s="8" t="inlineStr"/>
       <c r="F29" s="8" t="inlineStr"/>
@@ -932,7 +1074,11 @@
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="8" t="inlineStr"/>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>数据无法判断(需蒲公英核实报备情况)</t>
+        </is>
+      </c>
       <c r="D30" s="8" t="inlineStr"/>
       <c r="E30" s="8" t="inlineStr"/>
       <c r="F30" s="8" t="inlineStr"/>
@@ -944,7 +1090,11 @@
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr"/>
-      <c r="C31" s="8" t="inlineStr"/>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>2025-26集中放量，绑夏季面膜旺季</t>
+        </is>
+      </c>
       <c r="D31" s="8" t="inlineStr"/>
       <c r="E31" s="8" t="inlineStr"/>
       <c r="F31" s="8" t="inlineStr"/>
@@ -955,11 +1105,11 @@
           <t>⑤ 转化 / 口碑</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="15" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -968,7 +1118,11 @@
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr"/>
-      <c r="C33" s="8" t="inlineStr"/>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>重绑『日本药妆店/堂吉柯德/代购/伴手礼』线下+代购场景(偏站外)</t>
+        </is>
+      </c>
       <c r="D33" s="8" t="inlineStr"/>
       <c r="E33" s="8" t="inlineStr"/>
       <c r="F33" s="8" t="inlineStr"/>
@@ -980,7 +1134,11 @@
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr"/>
-      <c r="C34" s="8" t="inlineStr"/>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>内容多为『比价·哪个店最便宜』薅羊毛角度</t>
+        </is>
+      </c>
       <c r="D34" s="8" t="inlineStr"/>
       <c r="E34" s="8" t="inlineStr"/>
       <c r="F34" s="8" t="inlineStr"/>
@@ -992,7 +1150,11 @@
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="8" t="inlineStr"/>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>平价、补水、膜布薄而服帖、妆前好用、精华吸收快、抽拉装方便</t>
+        </is>
+      </c>
       <c r="D35" s="8" t="inlineStr"/>
       <c r="E35" s="8" t="inlineStr"/>
       <c r="F35" s="8" t="inlineStr"/>
@@ -1004,7 +1166,11 @@
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr"/>
-      <c r="C36" s="8" t="inlineStr"/>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>样本无评论数据(需另抓评论区)；可挖：功效平淡『只是补水』、同质化</t>
+        </is>
+      </c>
       <c r="D36" s="8" t="inlineStr"/>
       <c r="E36" s="8" t="inlineStr"/>
       <c r="F36" s="8" t="inlineStr"/>
@@ -1016,7 +1182,11 @@
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr"/>
-      <c r="C37" s="8" t="inlineStr"/>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>『怎么选』『平价』『药妆店哪买/哪便宜』(决策+价格+渠道)</t>
+        </is>
+      </c>
       <c r="D37" s="8" t="inlineStr"/>
       <c r="E37" s="8" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr"/>
@@ -1027,11 +1197,11 @@
           <t>⑥ 合规(化妆品红线)</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="15" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
@@ -1044,7 +1214,11 @@
           <t>普通化妆品</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr"/>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>普通化妆品(进口)</t>
+        </is>
+      </c>
       <c r="D39" s="8" t="inlineStr"/>
       <c r="E39" s="8" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr"/>
@@ -1060,7 +1234,11 @@
           <t>补水保湿(合规)·不宣称医疗</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr"/>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>存擦边：抗初老/淡痘印/K老/紧致等表述→我方勿照抄</t>
+        </is>
+      </c>
       <c r="D40" s="8" t="inlineStr"/>
       <c r="E40" s="8" t="inlineStr"/>
       <c r="F40" s="8" t="inlineStr"/>
@@ -1072,7 +1250,11 @@
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr"/>
-      <c r="C41" s="8" t="inlineStr"/>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>站外导流代购/微信；抗老医疗化表述；美白类需特证</t>
+        </is>
+      </c>
       <c r="D41" s="8" t="inlineStr"/>
       <c r="E41" s="8" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr"/>
@@ -1083,11 +1265,11 @@
           <t>⑦ 结论 / 差异化</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="15" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
@@ -1096,7 +1278,11 @@
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr"/>
-      <c r="C43" s="8" t="inlineStr"/>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>攻略型内容矩阵强+平价心智+日本原产背书+颜色速查记忆钩子</t>
+        </is>
+      </c>
       <c r="D43" s="8" t="inlineStr"/>
       <c r="E43" s="8" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr"/>
@@ -1108,7 +1294,11 @@
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr"/>
-      <c r="C44" s="8" t="inlineStr"/>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>视频内容少、官方运营弱靠自来水、内容同质化严重、无强复购运营</t>
+        </is>
+      </c>
       <c r="D44" s="8" t="inlineStr"/>
       <c r="E44" s="8" t="inlineStr"/>
       <c r="F44" s="8" t="inlineStr"/>
@@ -1120,7 +1310,11 @@
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr"/>
-      <c r="C45" s="8" t="inlineStr"/>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>主攻攻略合集+抢视频洼地+做Lululun横评蹭搜索+建自己颜色/肤质速查钩子</t>
+        </is>
+      </c>
       <c r="D45" s="8" t="inlineStr"/>
       <c r="E45" s="8" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr"/>
